--- a/课表格式模板.xlsx
+++ b/课表格式模板.xlsx
@@ -5,16 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\opencode_assistant\No.6-massageOfCourse\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\opencode_assistant\No.6-massageOfCourse\项目宣传\DailyReminder项目\完整版\待更新文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD56D62-3A10-4203-8462-FB1393C19ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC0514E-CC9F-4D89-9806-BFE76727FB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2520" yWindow="1390" windowWidth="15650" windowHeight="14290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="课表模板" sheetId="1" r:id="rId1"/>
-    <sheet name="填写说明" sheetId="2" r:id="rId2"/>
+    <sheet name="课程表" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -24,6 +23,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>系统</author>
+    <author>asus</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -36,11 +36,11 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>说明：第一列为节次，后续列为周一至周日</t>
+          <t>请保留标题和星期表头。课程信息填在星期列对应单元格中。</t>
         </r>
       </text>
     </comment>
-    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -50,11 +50,58 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>课程格式示例：课程名[编号] 周次 教室地点。编号可随意填写，如无编号可写[0]</t>
+          <t>推荐格式：课程名[课程编号] 序号
+周次 节次 教师[工号,职称] 地点
+上课班级信息可有可无，不会被识别出来。
+可以只修改课程名称、节数、上课地点、教师等关键信息，其他内容只做占位用途，删掉可能会影响识别效果</t>
         </r>
       </text>
     </comment>
-    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="C3" authorId="1" shapeId="0" xr:uid="{0970A4B6-9A0E-464B-802D-84554081AF99}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">单双周示例：1-16周(单)表示单周上课，1-16周(双)表示双周上课
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="1" shapeId="0" xr:uid="{139DB489-A097-4F43-91D7-432812311C2D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>同一单元格可写多个周次安排；不同课程安排用换行（Alt+回车）分隔。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="1" shapeId="0" xr:uid="{28F9F2B8-8B3D-4902-AE12-27B30E25BE11}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>不同周次同一课程用换行分隔</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -64,21 +111,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>单双周示例：1-16周(单)表示单周上课，1-16周(双)表示双周上课</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>同一单元格多门课程示例：不同周次同一课程用空行分隔</t>
+          <t>晚间课程请明确写“9-10节”，可避免节次误判。</t>
         </r>
       </text>
     </comment>
@@ -87,181 +120,109 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
-  <si>
-    <t>周一</t>
-  </si>
-  <si>
-    <t>周二</t>
-  </si>
-  <si>
-    <t>周三</t>
-  </si>
-  <si>
-    <t>周四</t>
-  </si>
-  <si>
-    <t>周五</t>
-  </si>
-  <si>
-    <t>周六</t>
-  </si>
-  <si>
-    <t>周日</t>
-  </si>
-  <si>
-    <t>第1-2节
-08:00-09:40</t>
-  </si>
-  <si>
-    <t>高等数学[00001]
-1-16周 张老师 一教101</t>
-  </si>
-  <si>
-    <t>大学物理[00002]
-1-16周(单) 李老师 科研楼201</t>
-  </si>
-  <si>
-    <t>第3-4节
-10:00-11:40</t>
-  </si>
-  <si>
-    <t>英语听说[00004]
-1-16周 赵老师 外语楼105</t>
-  </si>
-  <si>
-    <t>第5-6节
-14:00-15:40</t>
-  </si>
-  <si>
-    <t>数据结构[00005]
-1-16周 刘老师 一教203</t>
-  </si>
-  <si>
-    <t>体育[00006]
-1-16周 陈老师 操场</t>
-  </si>
-  <si>
-    <t>第7-8节
-16:00-17:40</t>
-  </si>
-  <si>
-    <t>线性代数[00007]
-1-16周(双) 周老师 一教305</t>
-  </si>
-  <si>
-    <t>第9-10节
-19:00-20:40</t>
-  </si>
-  <si>
-    <t>课表模板填写说明</t>
-  </si>
-  <si>
-    <t>一、基本格式</t>
-  </si>
-  <si>
-    <t>课程名称[编号]</t>
-  </si>
-  <si>
-    <t>编号可随意填写，如高等数学[001]，无编号可写[0]</t>
-  </si>
-  <si>
-    <t>周次</t>
-  </si>
-  <si>
-    <t>格式：1-16周 或 1-16周(单) 或 1-16周(双)</t>
-  </si>
-  <si>
-    <t>教师</t>
-  </si>
-  <si>
-    <t>教师姓名</t>
-  </si>
-  <si>
-    <t>地点</t>
-  </si>
-  <si>
-    <t>上课地点</t>
-  </si>
-  <si>
-    <t>二、完整示例</t>
-  </si>
-  <si>
-    <t>示例1</t>
-  </si>
-  <si>
-    <t>高等数学[001]</t>
-  </si>
-  <si>
-    <t>1-16周 张老师 一教101</t>
-  </si>
-  <si>
-    <t>示例2（单双周）</t>
-  </si>
-  <si>
-    <t>大学物理[002]</t>
-  </si>
-  <si>
-    <t>1-16周(单) 李老师 科研楼201</t>
-  </si>
-  <si>
-    <t>示例3（同一课程不同地点）</t>
-  </si>
-  <si>
-    <t>程序设计[003]</t>
-  </si>
-  <si>
-    <t>1-8周 王老师 机房301</t>
-  </si>
-  <si>
-    <t>9-16周 王老师 机房302</t>
-  </si>
-  <si>
-    <t>三、注意事项</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>每个单元格内的课程信息用换行分隔</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>同一单元格多门课程之间用空行分隔</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>编号不影响识别，可随意填写</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>周次格式必须正确，否则无法识别</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>删除示例课程后填入自己的课表</t>
-  </si>
-  <si>
-    <t>程序设计基础[00003]
-1-8周 王老师 机房301
-程序设计基础[00003]
-9-16周 王老师 机房302</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+  <si>
+    <t>2026-2027 学年 第X学期 课表模板（示例）</t>
+  </si>
+  <si>
+    <t>节次/星期</t>
+  </si>
+  <si>
+    <t>星期一</t>
+  </si>
+  <si>
+    <t>星期二</t>
+  </si>
+  <si>
+    <t>星期三</t>
+  </si>
+  <si>
+    <t>星期四</t>
+  </si>
+  <si>
+    <t>星期五</t>
+  </si>
+  <si>
+    <t>星期六</t>
+  </si>
+  <si>
+    <t>星期日</t>
+  </si>
+  <si>
+    <t>第一大节</t>
+  </si>
+  <si>
+    <t>第二大节</t>
+  </si>
+  <si>
+    <t>示例课程C[10003] 03
+1-8周 3-4节 示例教师C[90003,副教授] 示例教室C305
+9-16周 3-4节 示例教师C[90003,副教授] 示例教室C306</t>
+  </si>
+  <si>
+    <t>第三大节</t>
+  </si>
+  <si>
+    <t>第四大节</t>
+  </si>
+  <si>
+    <t>示例课程G[10007] 07
+1-16周 7-8节 示例教师G[90007,讲师] 示例教室G401</t>
+  </si>
+  <si>
+    <t>第五大节</t>
+  </si>
+  <si>
+    <t>示例课程H[10008] 08
+1-16周 9-10节 示例教师H[90008,副教授] 示例教室H806</t>
+  </si>
+  <si>
+    <t>示例课程I[10009] 09
+12-14周(双) 9-10节 示例教师I[90009,讲师] 示例教室I429</t>
+  </si>
+  <si>
+    <t>示例课程E[10005] 05
+2-16周(双) 5-6节 示例教师E[90005,教授] 示例教室E502</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>示例课程F[10006] 06
+1-16周 5-6节 示例教师F[90006,讲师] 示例场地F</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>示例课程k[10006] 06
+1-16周 7-8节 示例教师k[90006,讲师] 示例场地k</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>示例课程A[10001] 01
+1-16周 1-2节 示例教师A[90001,讲师] 示例教室A101
+示例班级A</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机网络[10007] 04
+1-8周 3-4节 王老师[22220262,助教（高校）] 一教1230
+9-16周 3-4节 王老师[22220262,助教（高校）] 一教1550</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>示例课程D[10004] 04
+1-16周 3-4节 示例教师D[90004,讲师] 示例教室D108</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>示例课程B[10002] 02
+1-16周(单) 1-2节 示例教师B[90002,讲师] 示例教室B201</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,26 +232,13 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -300,6 +248,28 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -311,16 +281,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -330,16 +300,55 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -347,20 +356,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -663,272 +681,233 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="8" width="18" customWidth="1"/>
+    <col min="1" max="8" width="25.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+    </row>
+    <row r="2" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <mergeCells count="41">
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="D7:D8"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="17.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="5"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>